--- a/Class files/employee_performance.xlsx
+++ b/Class files/employee_performance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel files\Class files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD82170-B50A-4CB8-AA4F-95E8852BDAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F6B248-A9CB-4B15-A203-042504242A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3748,23 +3748,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4097,7 +4097,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="7" t="s">
         <v>1197</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -4106,31 +4106,31 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="7" t="s">
         <v>1190</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="7" t="s">
         <v>1198</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="7" t="s">
         <v>1199</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="7" t="s">
         <v>1191</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="7" t="s">
         <v>1192</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="7" t="s">
         <v>1193</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="7" t="s">
         <v>1194</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="7" t="s">
         <v>1195</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -4213,11 +4213,11 @@
       <c r="R2" t="s">
         <v>17</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="U2" s="9" t="s">
         <v>1177</v>
       </c>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
       <c r="AF2" s="3" t="s">
         <v>18</v>
       </c>
@@ -4287,7 +4287,7 @@
       <c r="R3" t="s">
         <v>24</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="U3" t="s">
         <v>1178</v>
       </c>
       <c r="V3" s="8">
@@ -4364,7 +4364,7 @@
       <c r="R4" t="s">
         <v>32</v>
       </c>
-      <c r="U4" s="7" t="s">
+      <c r="U4" t="s">
         <v>1179</v>
       </c>
       <c r="V4" s="8">
@@ -4441,7 +4441,7 @@
       <c r="R5" t="s">
         <v>39</v>
       </c>
-      <c r="U5" s="7" t="s">
+      <c r="U5" t="s">
         <v>1180</v>
       </c>
       <c r="V5" s="8">
@@ -4518,7 +4518,7 @@
       <c r="R6" t="s">
         <v>46</v>
       </c>
-      <c r="U6" s="7" t="s">
+      <c r="U6" t="s">
         <v>1181</v>
       </c>
       <c r="V6" s="8">
@@ -4595,7 +4595,7 @@
       <c r="R7" t="s">
         <v>24</v>
       </c>
-      <c r="U7" s="7" t="s">
+      <c r="U7" t="s">
         <v>1182</v>
       </c>
       <c r="V7" s="8">
@@ -4672,7 +4672,7 @@
       <c r="R8" t="s">
         <v>58</v>
       </c>
-      <c r="U8" s="7" t="s">
+      <c r="U8" t="s">
         <v>1183</v>
       </c>
       <c r="V8" s="8">
@@ -4749,7 +4749,7 @@
       <c r="R9" t="s">
         <v>17</v>
       </c>
-      <c r="U9" s="7" t="s">
+      <c r="U9" t="s">
         <v>1184</v>
       </c>
       <c r="V9" s="8">
@@ -4826,7 +4826,7 @@
       <c r="R10" t="s">
         <v>70</v>
       </c>
-      <c r="U10" s="7" t="s">
+      <c r="U10" t="s">
         <v>1185</v>
       </c>
       <c r="V10" s="8">
@@ -4903,7 +4903,7 @@
       <c r="R11" t="s">
         <v>77</v>
       </c>
-      <c r="U11" s="9" t="s">
+      <c r="U11" s="6" t="s">
         <v>1186</v>
       </c>
       <c r="V11" s="8">
@@ -4980,11 +4980,11 @@
       <c r="R12" t="s">
         <v>24</v>
       </c>
-      <c r="U12" s="6" t="s">
+      <c r="U12" s="9" t="s">
         <v>1187</v>
       </c>
-      <c r="V12" s="6"/>
-      <c r="W12" s="6"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
       <c r="AF12" s="4" t="s">
         <v>84</v>
       </c>
@@ -5054,12 +5054,12 @@
       <c r="R13" t="s">
         <v>89</v>
       </c>
-      <c r="U13" s="9" t="s">
+      <c r="U13" s="6" t="s">
         <v>1188</v>
       </c>
       <c r="V13" s="10">
         <f ca="1">NOW()</f>
-        <v>46240.539438078704</v>
+        <v>46241.50055960648</v>
       </c>
       <c r="W13" s="8"/>
     </row>
@@ -5127,12 +5127,12 @@
       <c r="R14" t="s">
         <v>46</v>
       </c>
-      <c r="U14" s="9" t="s">
+      <c r="U14" s="6" t="s">
         <v>1189</v>
       </c>
       <c r="V14" s="11">
         <f ca="1">TODAY()</f>
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="W14" s="8"/>
     </row>
@@ -5200,10 +5200,13 @@
       <c r="R15" t="s">
         <v>39</v>
       </c>
-      <c r="U15" s="9" t="s">
+      <c r="U15" s="6" t="s">
         <v>1196</v>
       </c>
-      <c r="V15" s="11"/>
+      <c r="V15" s="11">
+        <f>DATE(2004,8,29)</f>
+        <v>38228</v>
+      </c>
       <c r="W15" s="8"/>
     </row>
     <row r="16" spans="1:33">
@@ -5270,9 +5273,8 @@
       <c r="R16" t="s">
         <v>32</v>
       </c>
-      <c r="U16" s="7"/>
-      <c r="V16" s="8"/>
-      <c r="W16" s="8"/>
+      <c r="V16" s="12"/>
+      <c r="W16" s="12"/>
     </row>
     <row r="17" spans="1:23">
       <c r="A17" t="s">
@@ -5338,9 +5340,8 @@
       <c r="R17" t="s">
         <v>32</v>
       </c>
-      <c r="U17" s="7"/>
-      <c r="V17" s="8"/>
-      <c r="W17" s="8"/>
+      <c r="V17" s="12"/>
+      <c r="W17" s="12"/>
     </row>
     <row r="18" spans="1:23">
       <c r="A18" t="s">
@@ -5406,9 +5407,8 @@
       <c r="R18" t="s">
         <v>77</v>
       </c>
-      <c r="U18" s="7"/>
-      <c r="V18" s="8"/>
-      <c r="W18" s="8"/>
+      <c r="V18" s="12"/>
+      <c r="W18" s="12"/>
     </row>
     <row r="19" spans="1:23">
       <c r="A19" t="s">
@@ -5474,9 +5474,8 @@
       <c r="R19" t="s">
         <v>115</v>
       </c>
-      <c r="U19" s="7"/>
-      <c r="V19" s="8"/>
-      <c r="W19" s="8"/>
+      <c r="V19" s="12"/>
+      <c r="W19" s="12"/>
     </row>
     <row r="20" spans="1:23">
       <c r="A20" t="s">
@@ -5542,9 +5541,8 @@
       <c r="R20" t="s">
         <v>24</v>
       </c>
-      <c r="U20" s="7"/>
-      <c r="V20" s="8"/>
-      <c r="W20" s="8"/>
+      <c r="V20" s="12"/>
+      <c r="W20" s="12"/>
     </row>
     <row r="21" spans="1:23">
       <c r="A21" t="s">
@@ -23812,17 +23810,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="V18:W18"/>
-    <mergeCell ref="V19:W19"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="V10:W10"/>
-    <mergeCell ref="V11:W11"/>
-    <mergeCell ref="U12:W12"/>
-    <mergeCell ref="V13:W13"/>
-    <mergeCell ref="V14:W14"/>
+  <mergeCells count="14">
+    <mergeCell ref="U2:W2"/>
     <mergeCell ref="V15:W15"/>
     <mergeCell ref="V3:W3"/>
     <mergeCell ref="V4:W4"/>
@@ -23831,7 +23820,11 @@
     <mergeCell ref="V7:W7"/>
     <mergeCell ref="V8:W8"/>
     <mergeCell ref="V9:W9"/>
-    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="V11:W11"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="V14:W14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
